--- a/output/shared/curva_ricostruita_dic2025.xlsx
+++ b/output/shared/curva_ricostruita_dic2025.xlsx
@@ -6,8 +6,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Bootstrap" sheetId="2" state="visible" r:id="rId1"/>
-    <sheet name="SmithWilson" sheetId="3" state="visible" r:id="rId2"/>
+    <sheet name="SmithWilson" sheetId="3" state="visible" r:id="rId1"/>
+    <sheet name="Bootstrap" sheetId="4" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -384,10 +384,10 @@
         <v>2.076</v>
       </c>
       <c r="D2" t="n">
-        <v>2.054745</v>
+        <v>2.114314</v>
       </c>
       <c r="E2" t="n">
-        <v>2.076</v>
+        <v>2.136824</v>
       </c>
     </row>
     <row r="3">
@@ -401,10 +401,10 @@
         <v>2.163032</v>
       </c>
       <c r="D3" t="n">
-        <v>2.225195</v>
+        <v>2.361622</v>
       </c>
       <c r="E3" t="n">
-        <v>2.250137</v>
+        <v>2.38973</v>
       </c>
     </row>
     <row r="4">
@@ -418,10 +418,10 @@
         <v>2.282858</v>
       </c>
       <c r="D4" t="n">
-        <v>2.491632</v>
+        <v>2.590168</v>
       </c>
       <c r="E4" t="n">
-        <v>2.522932</v>
+        <v>2.624004</v>
       </c>
     </row>
     <row r="5">
@@ -435,10 +435,10 @@
         <v>2.386292</v>
       </c>
       <c r="D5" t="n">
-        <v>2.661487</v>
+        <v>2.736766</v>
       </c>
       <c r="E5" t="n">
-        <v>2.697221</v>
+        <v>2.77456</v>
       </c>
     </row>
     <row r="6">
@@ -452,10 +452,10 @@
         <v>2.478759</v>
       </c>
       <c r="D6" t="n">
-        <v>2.809621</v>
+        <v>2.876139</v>
       </c>
       <c r="E6" t="n">
-        <v>2.849463</v>
+        <v>2.917899</v>
       </c>
     </row>
     <row r="7">
@@ -469,10 +469,10 @@
         <v>2.564868</v>
       </c>
       <c r="D7" t="n">
-        <v>2.952482</v>
+        <v>3.044924</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9965</v>
+        <v>3.091756</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         <v>2.651038</v>
       </c>
       <c r="D8" t="n">
-        <v>3.120388</v>
+        <v>3.16284</v>
       </c>
       <c r="E8" t="n">
-        <v>3.169583</v>
+        <v>3.213389</v>
       </c>
     </row>
     <row r="9">
@@ -503,10 +503,10 @@
         <v>2.72399</v>
       </c>
       <c r="D9" t="n">
-        <v>3.18485</v>
+        <v>3.219364</v>
       </c>
       <c r="E9" t="n">
-        <v>3.236109</v>
+        <v>3.271746</v>
       </c>
     </row>
     <row r="10">
@@ -520,10 +520,10 @@
         <v>2.792521</v>
       </c>
       <c r="D10" t="n">
-        <v>3.28777</v>
+        <v>3.377617</v>
       </c>
       <c r="E10" t="n">
-        <v>3.342415</v>
+        <v>3.435306</v>
       </c>
     </row>
     <row r="11">
@@ -537,10 +537,10 @@
         <v>2.863084</v>
       </c>
       <c r="D11" t="n">
-        <v>3.440462</v>
+        <v>3.454728</v>
       </c>
       <c r="E11" t="n">
-        <v>3.500331</v>
+        <v>3.515097</v>
       </c>
     </row>
     <row r="12">
@@ -554,10 +554,10 @@
         <v>2.920817</v>
       </c>
       <c r="D12" t="n">
-        <v>3.44008</v>
+        <v>3.445216</v>
       </c>
       <c r="E12" t="n">
-        <v>3.499935</v>
+        <v>3.505251</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>2.974789</v>
       </c>
       <c r="D13" t="n">
-        <v>3.508089</v>
+        <v>3.60903</v>
       </c>
       <c r="E13" t="n">
-        <v>3.570349</v>
+        <v>3.674946</v>
       </c>
     </row>
     <row r="14">
@@ -588,10 +588,10 @@
         <v>3.03333</v>
       </c>
       <c r="D14" t="n">
-        <v>3.67024</v>
+        <v>3.653169</v>
       </c>
       <c r="E14" t="n">
-        <v>3.738425</v>
+        <v>3.720718</v>
       </c>
     </row>
     <row r="15">
@@ -599,16 +599,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3.026722</v>
+        <v>3.030049</v>
       </c>
       <c r="C15" t="n">
-        <v>3.072993</v>
+        <v>3.076422</v>
       </c>
       <c r="D15" t="n">
-        <v>3.527066</v>
+        <v>3.510313</v>
       </c>
       <c r="E15" t="n">
-        <v>3.590004</v>
+        <v>3.572651</v>
       </c>
     </row>
     <row r="16">
@@ -616,16 +616,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3.060078</v>
+        <v>3.059983</v>
       </c>
       <c r="C16" t="n">
-        <v>3.10738</v>
+        <v>3.107282</v>
       </c>
       <c r="D16" t="n">
-        <v>3.527066</v>
+        <v>3.463686</v>
       </c>
       <c r="E16" t="n">
-        <v>3.590004</v>
+        <v>3.524371</v>
       </c>
     </row>
     <row r="17">
@@ -633,16 +633,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3.084722</v>
+        <v>3.085215</v>
       </c>
       <c r="C17" t="n">
-        <v>3.132792</v>
+        <v>3.133301</v>
       </c>
       <c r="D17" t="n">
-        <v>3.454378</v>
+        <v>3.463208</v>
       </c>
       <c r="E17" t="n">
-        <v>3.514735</v>
+        <v>3.523875</v>
       </c>
     </row>
     <row r="18">
@@ -650,16 +650,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3.106466</v>
+        <v>3.107363</v>
       </c>
       <c r="C18" t="n">
-        <v>3.155221</v>
+        <v>3.156146</v>
       </c>
       <c r="D18" t="n">
-        <v>3.454378</v>
+        <v>3.459761</v>
       </c>
       <c r="E18" t="n">
-        <v>3.514735</v>
+        <v>3.520307</v>
       </c>
     </row>
     <row r="19">
@@ -667,16 +667,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3.125795</v>
+        <v>3.126778</v>
       </c>
       <c r="C19" t="n">
-        <v>3.175161</v>
+        <v>3.176175</v>
       </c>
       <c r="D19" t="n">
-        <v>3.454378</v>
+        <v>3.453427</v>
       </c>
       <c r="E19" t="n">
-        <v>3.514735</v>
+        <v>3.513751</v>
       </c>
     </row>
     <row r="20">
@@ -684,16 +684,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.143089</v>
+        <v>3.143741</v>
       </c>
       <c r="C20" t="n">
-        <v>3.193005</v>
+        <v>3.193679</v>
       </c>
       <c r="D20" t="n">
-        <v>3.454378</v>
+        <v>3.444269</v>
       </c>
       <c r="E20" t="n">
-        <v>3.514735</v>
+        <v>3.50427</v>
       </c>
     </row>
     <row r="21">
@@ -701,16 +701,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3.158653</v>
+        <v>3.158481</v>
       </c>
       <c r="C21" t="n">
-        <v>3.209068</v>
+        <v>3.20889</v>
       </c>
       <c r="D21" t="n">
-        <v>3.454378</v>
+        <v>3.432332</v>
       </c>
       <c r="E21" t="n">
-        <v>3.514735</v>
+        <v>3.491917</v>
       </c>
     </row>
     <row r="22">
@@ -718,16 +718,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3.161905</v>
+        <v>3.171212</v>
       </c>
       <c r="C22" t="n">
-        <v>3.212424</v>
+        <v>3.22203</v>
       </c>
       <c r="D22" t="n">
-        <v>3.226932</v>
+        <v>3.419465</v>
       </c>
       <c r="E22" t="n">
-        <v>3.279562</v>
+        <v>3.478601</v>
       </c>
     </row>
     <row r="23">
@@ -735,16 +735,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3.165023</v>
+        <v>3.18222</v>
       </c>
       <c r="C23" t="n">
-        <v>3.215643</v>
+        <v>3.233394</v>
       </c>
       <c r="D23" t="n">
-        <v>3.230518</v>
+        <v>3.407471</v>
       </c>
       <c r="E23" t="n">
-        <v>3.283266</v>
+        <v>3.46619</v>
       </c>
     </row>
     <row r="24">
@@ -752,16 +752,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3.167999</v>
+        <v>3.191768</v>
       </c>
       <c r="C24" t="n">
-        <v>3.218714</v>
+        <v>3.243251</v>
       </c>
       <c r="D24" t="n">
-        <v>3.233455</v>
+        <v>3.396291</v>
       </c>
       <c r="E24" t="n">
-        <v>3.286299</v>
+        <v>3.454624</v>
       </c>
     </row>
     <row r="25">
@@ -769,16 +769,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3.170826</v>
+        <v>3.20007</v>
       </c>
       <c r="C25" t="n">
-        <v>3.221632</v>
+        <v>3.251823</v>
       </c>
       <c r="D25" t="n">
-        <v>3.235859</v>
+        <v>3.385874</v>
       </c>
       <c r="E25" t="n">
-        <v>3.288783</v>
+        <v>3.443847</v>
       </c>
     </row>
     <row r="26">
@@ -786,16 +786,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3.173506</v>
+        <v>3.207306</v>
       </c>
       <c r="C26" t="n">
-        <v>3.224399</v>
+        <v>3.259294</v>
       </c>
       <c r="D26" t="n">
-        <v>3.237828</v>
+        <v>3.37617</v>
       </c>
       <c r="E26" t="n">
-        <v>3.290816</v>
+        <v>3.433809</v>
       </c>
     </row>
     <row r="27">
@@ -803,16 +803,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3.176042</v>
+        <v>3.213625</v>
       </c>
       <c r="C27" t="n">
-        <v>3.227017</v>
+        <v>3.265819</v>
       </c>
       <c r="D27" t="n">
-        <v>3.23944</v>
+        <v>3.367131</v>
       </c>
       <c r="E27" t="n">
-        <v>3.292481</v>
+        <v>3.42446</v>
       </c>
     </row>
     <row r="28">
@@ -820,16 +820,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3.178439</v>
+        <v>3.219152</v>
       </c>
       <c r="C28" t="n">
-        <v>3.229491</v>
+        <v>3.271527</v>
       </c>
       <c r="D28" t="n">
-        <v>3.240759</v>
+        <v>3.358713</v>
       </c>
       <c r="E28" t="n">
-        <v>3.293844</v>
+        <v>3.415755</v>
       </c>
     </row>
     <row r="29">
@@ -837,16 +837,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3.180703</v>
+        <v>3.223995</v>
       </c>
       <c r="C29" t="n">
-        <v>3.231828</v>
+        <v>3.276529</v>
       </c>
       <c r="D29" t="n">
-        <v>3.24184</v>
+        <v>3.350876</v>
       </c>
       <c r="E29" t="n">
-        <v>3.29496</v>
+        <v>3.40765</v>
       </c>
     </row>
     <row r="30">
@@ -854,16 +854,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3.182842</v>
+        <v>3.228243</v>
       </c>
       <c r="C30" t="n">
-        <v>3.234036</v>
+        <v>3.280916</v>
       </c>
       <c r="D30" t="n">
-        <v>3.242724</v>
+        <v>3.343579</v>
       </c>
       <c r="E30" t="n">
-        <v>3.295873</v>
+        <v>3.400105</v>
       </c>
     </row>
     <row r="31">
@@ -871,16 +871,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3.184862</v>
+        <v>3.231973</v>
       </c>
       <c r="C31" t="n">
-        <v>3.236122</v>
+        <v>3.284768</v>
       </c>
       <c r="D31" t="n">
-        <v>3.243448</v>
+        <v>3.336787</v>
       </c>
       <c r="E31" t="n">
-        <v>3.296621</v>
+        <v>3.393083</v>
       </c>
     </row>
     <row r="32">
@@ -888,16 +888,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3.186771</v>
+        <v>3.235251</v>
       </c>
       <c r="C32" t="n">
-        <v>3.238092</v>
+        <v>3.288154</v>
       </c>
       <c r="D32" t="n">
-        <v>3.244041</v>
+        <v>3.330467</v>
       </c>
       <c r="E32" t="n">
-        <v>3.297234</v>
+        <v>3.386547</v>
       </c>
     </row>
     <row r="33">
@@ -905,16 +905,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3.188576</v>
+        <v>3.238133</v>
       </c>
       <c r="C33" t="n">
-        <v>3.239956</v>
+        <v>3.291131</v>
       </c>
       <c r="D33" t="n">
-        <v>3.244527</v>
+        <v>3.324584</v>
       </c>
       <c r="E33" t="n">
-        <v>3.297735</v>
+        <v>3.380466</v>
       </c>
     </row>
     <row r="34">
@@ -922,16 +922,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3.190284</v>
+        <v>3.240669</v>
       </c>
       <c r="C34" t="n">
-        <v>3.241719</v>
+        <v>3.293751</v>
       </c>
       <c r="D34" t="n">
-        <v>3.244924</v>
+        <v>3.319111</v>
       </c>
       <c r="E34" t="n">
-        <v>3.298146</v>
+        <v>3.374808</v>
       </c>
     </row>
     <row r="35">
@@ -939,16 +939,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3.1919</v>
+        <v>3.2429</v>
       </c>
       <c r="C35" t="n">
-        <v>3.243388</v>
+        <v>3.296055</v>
       </c>
       <c r="D35" t="n">
-        <v>3.245249</v>
+        <v>3.314019</v>
       </c>
       <c r="E35" t="n">
-        <v>3.298482</v>
+        <v>3.369545</v>
       </c>
     </row>
     <row r="36">
@@ -956,16 +956,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3.193432</v>
+        <v>3.244864</v>
       </c>
       <c r="C36" t="n">
-        <v>3.244969</v>
+        <v>3.298084</v>
       </c>
       <c r="D36" t="n">
-        <v>3.245516</v>
+        <v>3.309283</v>
       </c>
       <c r="E36" t="n">
-        <v>3.298757</v>
+        <v>3.364648</v>
       </c>
     </row>
     <row r="37">
@@ -973,16 +973,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3.194885</v>
+        <v>3.246591</v>
       </c>
       <c r="C37" t="n">
-        <v>3.246469</v>
+        <v>3.299868</v>
       </c>
       <c r="D37" t="n">
-        <v>3.245734</v>
+        <v>3.304877</v>
       </c>
       <c r="E37" t="n">
-        <v>3.298982</v>
+        <v>3.360094</v>
       </c>
     </row>
     <row r="38">
@@ -990,16 +990,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3.196264</v>
+        <v>3.248111</v>
       </c>
       <c r="C38" t="n">
-        <v>3.247893</v>
+        <v>3.301437</v>
       </c>
       <c r="D38" t="n">
-        <v>3.245912</v>
+        <v>3.300778</v>
       </c>
       <c r="E38" t="n">
-        <v>3.299167</v>
+        <v>3.355859</v>
       </c>
     </row>
     <row r="39">
@@ -1007,16 +1007,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3.197574</v>
+        <v>3.249446</v>
       </c>
       <c r="C39" t="n">
-        <v>3.249246</v>
+        <v>3.302817</v>
       </c>
       <c r="D39" t="n">
-        <v>3.246059</v>
+        <v>3.296967</v>
       </c>
       <c r="E39" t="n">
-        <v>3.299318</v>
+        <v>3.351919</v>
       </c>
     </row>
     <row r="40">
@@ -1024,16 +1024,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3.198821</v>
+        <v>3.250618</v>
       </c>
       <c r="C40" t="n">
-        <v>3.250533</v>
+        <v>3.304028</v>
       </c>
       <c r="D40" t="n">
-        <v>3.246178</v>
+        <v>3.293423</v>
       </c>
       <c r="E40" t="n">
-        <v>3.299441</v>
+        <v>3.348256</v>
       </c>
     </row>
     <row r="41">
@@ -1041,16 +1041,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3.200007</v>
+        <v>3.251647</v>
       </c>
       <c r="C41" t="n">
-        <v>3.251758</v>
+        <v>3.30509</v>
       </c>
       <c r="D41" t="n">
-        <v>3.246276</v>
+        <v>3.290127</v>
       </c>
       <c r="E41" t="n">
-        <v>3.299543</v>
+        <v>3.34485</v>
       </c>
     </row>
     <row r="42">
@@ -1058,16 +1058,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3.201138</v>
+        <v>3.252547</v>
       </c>
       <c r="C42" t="n">
-        <v>3.252925</v>
+        <v>3.306021</v>
       </c>
       <c r="D42" t="n">
-        <v>3.246357</v>
+        <v>3.287063</v>
       </c>
       <c r="E42" t="n">
-        <v>3.299626</v>
+        <v>3.341683</v>
       </c>
     </row>
     <row r="43">
@@ -1075,16 +1075,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3.202216</v>
+        <v>3.253335</v>
       </c>
       <c r="C43" t="n">
-        <v>3.254038</v>
+        <v>3.306834</v>
       </c>
       <c r="D43" t="n">
-        <v>3.246422</v>
+        <v>3.284213</v>
       </c>
       <c r="E43" t="n">
-        <v>3.299693</v>
+        <v>3.338739</v>
       </c>
     </row>
     <row r="44">
@@ -1092,16 +1092,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3.203245</v>
+        <v>3.254022</v>
       </c>
       <c r="C44" t="n">
-        <v>3.255101</v>
+        <v>3.307544</v>
       </c>
       <c r="D44" t="n">
-        <v>3.246476</v>
+        <v>3.281564</v>
       </c>
       <c r="E44" t="n">
-        <v>3.299749</v>
+        <v>3.336001</v>
       </c>
     </row>
     <row r="45">
@@ -1109,16 +1109,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3.204229</v>
+        <v>3.254619</v>
       </c>
       <c r="C45" t="n">
-        <v>3.256117</v>
+        <v>3.308161</v>
       </c>
       <c r="D45" t="n">
-        <v>3.24652</v>
+        <v>3.279102</v>
       </c>
       <c r="E45" t="n">
-        <v>3.299795</v>
+        <v>3.333457</v>
       </c>
     </row>
     <row r="46">
@@ -1126,16 +1126,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3.205169</v>
+        <v>3.255138</v>
       </c>
       <c r="C46" t="n">
-        <v>3.257088</v>
+        <v>3.308697</v>
       </c>
       <c r="D46" t="n">
-        <v>3.246556</v>
+        <v>3.276812</v>
       </c>
       <c r="E46" t="n">
-        <v>3.299832</v>
+        <v>3.331091</v>
       </c>
     </row>
     <row r="47">
@@ -1143,16 +1143,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3.20607</v>
+        <v>3.255586</v>
       </c>
       <c r="C47" t="n">
-        <v>3.258018</v>
+        <v>3.30916</v>
       </c>
       <c r="D47" t="n">
-        <v>3.246586</v>
+        <v>3.274684</v>
       </c>
       <c r="E47" t="n">
-        <v>3.299862</v>
+        <v>3.328892</v>
       </c>
     </row>
     <row r="48">
@@ -1160,16 +1160,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3.206932</v>
+        <v>3.255971</v>
       </c>
       <c r="C48" t="n">
-        <v>3.258908</v>
+        <v>3.309557</v>
       </c>
       <c r="D48" t="n">
-        <v>3.24661</v>
+        <v>3.272706</v>
       </c>
       <c r="E48" t="n">
-        <v>3.299887</v>
+        <v>3.326848</v>
       </c>
     </row>
     <row r="49">
@@ -1177,16 +1177,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3.207759</v>
+        <v>3.2563</v>
       </c>
       <c r="C49" t="n">
-        <v>3.259762</v>
+        <v>3.309897</v>
       </c>
       <c r="D49" t="n">
-        <v>3.24663</v>
+        <v>3.270867</v>
       </c>
       <c r="E49" t="n">
-        <v>3.299908</v>
+        <v>3.324948</v>
       </c>
     </row>
     <row r="50">
@@ -1194,16 +1194,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3.208553</v>
+        <v>3.25658</v>
       </c>
       <c r="C50" t="n">
-        <v>3.260582</v>
+        <v>3.310186</v>
       </c>
       <c r="D50" t="n">
-        <v>3.246646</v>
+        <v>3.269158</v>
       </c>
       <c r="E50" t="n">
-        <v>3.299924</v>
+        <v>3.323182</v>
       </c>
     </row>
     <row r="51">
@@ -1211,16 +1211,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3.209315</v>
+        <v>3.256815</v>
       </c>
       <c r="C51" t="n">
-        <v>3.261369</v>
+        <v>3.31043</v>
       </c>
       <c r="D51" t="n">
-        <v>3.246659</v>
+        <v>3.26757</v>
       </c>
       <c r="E51" t="n">
-        <v>3.299938</v>
+        <v>3.321541</v>
       </c>
     </row>
     <row r="52">
@@ -1228,16 +1228,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3.210047</v>
+        <v>3.257011</v>
       </c>
       <c r="C52" t="n">
-        <v>3.262125</v>
+        <v>3.310632</v>
       </c>
       <c r="D52" t="n">
-        <v>3.24667</v>
+        <v>3.266094</v>
       </c>
       <c r="E52" t="n">
-        <v>3.299949</v>
+        <v>3.320016</v>
       </c>
     </row>
     <row r="53">
@@ -1245,16 +1245,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3.210752</v>
+        <v>3.257173</v>
       </c>
       <c r="C53" t="n">
-        <v>3.262853</v>
+        <v>3.310799</v>
       </c>
       <c r="D53" t="n">
-        <v>3.246679</v>
+        <v>3.264722</v>
       </c>
       <c r="E53" t="n">
-        <v>3.299959</v>
+        <v>3.318599</v>
       </c>
     </row>
     <row r="54">
@@ -1262,16 +1262,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>3.21143</v>
+        <v>3.257303</v>
       </c>
       <c r="C54" t="n">
-        <v>3.263553</v>
+        <v>3.310934</v>
       </c>
       <c r="D54" t="n">
-        <v>3.246686</v>
+        <v>3.263447</v>
       </c>
       <c r="E54" t="n">
-        <v>3.299966</v>
+        <v>3.317281</v>
       </c>
     </row>
     <row r="55">
@@ -1279,16 +1279,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3.212083</v>
+        <v>3.257405</v>
       </c>
       <c r="C55" t="n">
-        <v>3.264227</v>
+        <v>3.31104</v>
       </c>
       <c r="D55" t="n">
-        <v>3.246692</v>
+        <v>3.262262</v>
       </c>
       <c r="E55" t="n">
-        <v>3.299972</v>
+        <v>3.316057</v>
       </c>
     </row>
     <row r="56">
@@ -1296,16 +1296,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>3.212712</v>
+        <v>3.257484</v>
       </c>
       <c r="C56" t="n">
-        <v>3.264877</v>
+        <v>3.31112</v>
       </c>
       <c r="D56" t="n">
-        <v>3.246697</v>
+        <v>3.261161</v>
       </c>
       <c r="E56" t="n">
-        <v>3.299977</v>
+        <v>3.314919</v>
       </c>
     </row>
     <row r="57">
@@ -1313,16 +1313,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>3.213319</v>
+        <v>3.25754</v>
       </c>
       <c r="C57" t="n">
-        <v>3.265504</v>
+        <v>3.311179</v>
       </c>
       <c r="D57" t="n">
-        <v>3.246701</v>
+        <v>3.260137</v>
       </c>
       <c r="E57" t="n">
-        <v>3.299981</v>
+        <v>3.313862</v>
       </c>
     </row>
     <row r="58">
@@ -1330,16 +1330,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>3.213905</v>
+        <v>3.257577</v>
       </c>
       <c r="C58" t="n">
-        <v>3.266108</v>
+        <v>3.311217</v>
       </c>
       <c r="D58" t="n">
-        <v>3.246704</v>
+        <v>3.259186</v>
       </c>
       <c r="E58" t="n">
-        <v>3.299985</v>
+        <v>3.31288</v>
       </c>
     </row>
     <row r="59">
@@ -1347,16 +1347,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>3.21447</v>
+        <v>3.257597</v>
       </c>
       <c r="C59" t="n">
-        <v>3.266693</v>
+        <v>3.311238</v>
       </c>
       <c r="D59" t="n">
-        <v>3.246707</v>
+        <v>3.258303</v>
       </c>
       <c r="E59" t="n">
-        <v>3.299988</v>
+        <v>3.311967</v>
       </c>
     </row>
     <row r="60">
@@ -1364,16 +1364,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>3.215017</v>
+        <v>3.257602</v>
       </c>
       <c r="C60" t="n">
-        <v>3.267257</v>
+        <v>3.311243</v>
       </c>
       <c r="D60" t="n">
-        <v>3.246709</v>
+        <v>3.257482</v>
       </c>
       <c r="E60" t="n">
-        <v>3.29999</v>
+        <v>3.311118</v>
       </c>
     </row>
     <row r="61">
@@ -1381,16 +1381,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>3.215545</v>
+        <v>3.257594</v>
       </c>
       <c r="C61" t="n">
-        <v>3.267802</v>
+        <v>3.311234</v>
       </c>
       <c r="D61" t="n">
-        <v>3.246711</v>
+        <v>3.256719</v>
       </c>
       <c r="E61" t="n">
-        <v>3.299992</v>
+        <v>3.31033</v>
       </c>
     </row>
     <row r="62">
@@ -1398,16 +1398,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>3.216056</v>
+        <v>3.257573</v>
       </c>
       <c r="C62" t="n">
-        <v>3.26833</v>
+        <v>3.311213</v>
       </c>
       <c r="D62" t="n">
-        <v>3.246712</v>
+        <v>3.25601</v>
       </c>
       <c r="E62" t="n">
-        <v>3.299993</v>
+        <v>3.309598</v>
       </c>
     </row>
     <row r="63">
@@ -1415,16 +1415,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>3.21655</v>
+        <v>3.257543</v>
       </c>
       <c r="C63" t="n">
-        <v>3.268841</v>
+        <v>3.311182</v>
       </c>
       <c r="D63" t="n">
-        <v>3.246714</v>
+        <v>3.255351</v>
       </c>
       <c r="E63" t="n">
-        <v>3.299994</v>
+        <v>3.308917</v>
       </c>
     </row>
     <row r="64">
@@ -1432,16 +1432,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>3.217029</v>
+        <v>3.257503</v>
       </c>
       <c r="C64" t="n">
-        <v>3.269335</v>
+        <v>3.311141</v>
       </c>
       <c r="D64" t="n">
-        <v>3.246715</v>
+        <v>3.254739</v>
       </c>
       <c r="E64" t="n">
-        <v>3.299995</v>
+        <v>3.308285</v>
       </c>
     </row>
     <row r="65">
@@ -1449,16 +1449,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>3.217493</v>
+        <v>3.257455</v>
       </c>
       <c r="C65" t="n">
-        <v>3.269814</v>
+        <v>3.311091</v>
       </c>
       <c r="D65" t="n">
-        <v>3.246715</v>
+        <v>3.25417</v>
       </c>
       <c r="E65" t="n">
-        <v>3.299996</v>
+        <v>3.307697</v>
       </c>
     </row>
     <row r="66">
@@ -1466,16 +1466,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>3.217943</v>
+        <v>3.257401</v>
       </c>
       <c r="C66" t="n">
-        <v>3.270278</v>
+        <v>3.311035</v>
       </c>
       <c r="D66" t="n">
-        <v>3.246716</v>
+        <v>3.253642</v>
       </c>
       <c r="E66" t="n">
-        <v>3.299997</v>
+        <v>3.307151</v>
       </c>
     </row>
     <row r="67">
@@ -1483,16 +1483,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>3.218379</v>
+        <v>3.25734</v>
       </c>
       <c r="C67" t="n">
-        <v>3.270729</v>
+        <v>3.310972</v>
       </c>
       <c r="D67" t="n">
-        <v>3.246717</v>
+        <v>3.253151</v>
       </c>
       <c r="E67" t="n">
-        <v>3.299997</v>
+        <v>3.306644</v>
       </c>
     </row>
     <row r="68">
@@ -1500,16 +1500,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>3.218802</v>
+        <v>3.257274</v>
       </c>
       <c r="C68" t="n">
-        <v>3.271165</v>
+        <v>3.310904</v>
       </c>
       <c r="D68" t="n">
-        <v>3.246717</v>
+        <v>3.252695</v>
       </c>
       <c r="E68" t="n">
-        <v>3.299998</v>
+        <v>3.306173</v>
       </c>
     </row>
     <row r="69">
@@ -1517,16 +1517,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>3.219212</v>
+        <v>3.257204</v>
       </c>
       <c r="C69" t="n">
-        <v>3.271589</v>
+        <v>3.310831</v>
       </c>
       <c r="D69" t="n">
-        <v>3.246717</v>
+        <v>3.252271</v>
       </c>
       <c r="E69" t="n">
-        <v>3.299998</v>
+        <v>3.305735</v>
       </c>
     </row>
     <row r="70">
@@ -1534,16 +1534,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>3.219611</v>
+        <v>3.257129</v>
       </c>
       <c r="C70" t="n">
-        <v>3.272001</v>
+        <v>3.310754</v>
       </c>
       <c r="D70" t="n">
-        <v>3.246718</v>
+        <v>3.251877</v>
       </c>
       <c r="E70" t="n">
-        <v>3.299999</v>
+        <v>3.305328</v>
       </c>
     </row>
     <row r="71">
@@ -1551,16 +1551,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>3.219998</v>
+        <v>3.257052</v>
       </c>
       <c r="C71" t="n">
-        <v>3.272401</v>
+        <v>3.310674</v>
       </c>
       <c r="D71" t="n">
-        <v>3.246718</v>
+        <v>3.251511</v>
       </c>
       <c r="E71" t="n">
-        <v>3.299999</v>
+        <v>3.30495</v>
       </c>
     </row>
     <row r="72">
@@ -1568,16 +1568,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>3.220374</v>
+        <v>3.256971</v>
       </c>
       <c r="C72" t="n">
-        <v>3.27279</v>
+        <v>3.310591</v>
       </c>
       <c r="D72" t="n">
-        <v>3.246718</v>
+        <v>3.251171</v>
       </c>
       <c r="E72" t="n">
-        <v>3.299999</v>
+        <v>3.304599</v>
       </c>
     </row>
     <row r="73">
@@ -1585,16 +1585,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>3.22074</v>
+        <v>3.256888</v>
       </c>
       <c r="C73" t="n">
-        <v>3.273167</v>
+        <v>3.310505</v>
       </c>
       <c r="D73" t="n">
-        <v>3.246718</v>
+        <v>3.250855</v>
       </c>
       <c r="E73" t="n">
-        <v>3.299999</v>
+        <v>3.304273</v>
       </c>
     </row>
     <row r="74">
@@ -1602,16 +1602,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>3.221096</v>
+        <v>3.256804</v>
       </c>
       <c r="C74" t="n">
-        <v>3.273535</v>
+        <v>3.310418</v>
       </c>
       <c r="D74" t="n">
-        <v>3.246718</v>
+        <v>3.250562</v>
       </c>
       <c r="E74" t="n">
-        <v>3.299999</v>
+        <v>3.30397</v>
       </c>
     </row>
     <row r="75">
@@ -1619,16 +1619,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>3.221442</v>
+        <v>3.256717</v>
       </c>
       <c r="C75" t="n">
-        <v>3.273892</v>
+        <v>3.310329</v>
       </c>
       <c r="D75" t="n">
-        <v>3.246719</v>
+        <v>3.250289</v>
       </c>
       <c r="E75" t="n">
-        <v>3.299999</v>
+        <v>3.303688</v>
       </c>
     </row>
     <row r="76">
@@ -1636,16 +1636,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>3.221779</v>
+        <v>3.25663</v>
       </c>
       <c r="C76" t="n">
-        <v>3.274241</v>
+        <v>3.310239</v>
       </c>
       <c r="D76" t="n">
-        <v>3.246719</v>
+        <v>3.250036</v>
       </c>
       <c r="E76" t="n">
-        <v>3.3</v>
+        <v>3.303426</v>
       </c>
     </row>
     <row r="77">
@@ -1653,16 +1653,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>3.222107</v>
+        <v>3.256542</v>
       </c>
       <c r="C77" t="n">
-        <v>3.274579</v>
+        <v>3.310147</v>
       </c>
       <c r="D77" t="n">
-        <v>3.246719</v>
+        <v>3.2498</v>
       </c>
       <c r="E77" t="n">
-        <v>3.3</v>
+        <v>3.303183</v>
       </c>
     </row>
     <row r="78">
@@ -1670,16 +1670,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>3.222427</v>
+        <v>3.256453</v>
       </c>
       <c r="C78" t="n">
-        <v>3.27491</v>
+        <v>3.310055</v>
       </c>
       <c r="D78" t="n">
-        <v>3.246719</v>
+        <v>3.249582</v>
       </c>
       <c r="E78" t="n">
-        <v>3.3</v>
+        <v>3.302957</v>
       </c>
     </row>
     <row r="79">
@@ -1687,16 +1687,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>3.222739</v>
+        <v>3.256363</v>
       </c>
       <c r="C79" t="n">
-        <v>3.275231</v>
+        <v>3.309963</v>
       </c>
       <c r="D79" t="n">
-        <v>3.246719</v>
+        <v>3.249379</v>
       </c>
       <c r="E79" t="n">
-        <v>3.3</v>
+        <v>3.302747</v>
       </c>
     </row>
     <row r="80">
@@ -1704,16 +1704,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>3.223042</v>
+        <v>3.256274</v>
       </c>
       <c r="C80" t="n">
-        <v>3.275545</v>
+        <v>3.30987</v>
       </c>
       <c r="D80" t="n">
-        <v>3.246719</v>
+        <v>3.24919</v>
       </c>
       <c r="E80" t="n">
-        <v>3.3</v>
+        <v>3.302552</v>
       </c>
     </row>
     <row r="81">
@@ -1721,16 +1721,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>3.223338</v>
+        <v>3.256184</v>
       </c>
       <c r="C81" t="n">
-        <v>3.27585</v>
+        <v>3.309778</v>
       </c>
       <c r="D81" t="n">
-        <v>3.246719</v>
+        <v>3.249015</v>
       </c>
       <c r="E81" t="n">
-        <v>3.3</v>
+        <v>3.302371</v>
       </c>
     </row>
     <row r="82">
@@ -1738,16 +1738,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>3.223627</v>
+        <v>3.256094</v>
       </c>
       <c r="C82" t="n">
-        <v>3.276148</v>
+        <v>3.309685</v>
       </c>
       <c r="D82" t="n">
-        <v>3.246719</v>
+        <v>3.248852</v>
       </c>
       <c r="E82" t="n">
-        <v>3.3</v>
+        <v>3.302203</v>
       </c>
     </row>
     <row r="83">
@@ -1755,16 +1755,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>3.223908</v>
+        <v>3.256005</v>
       </c>
       <c r="C83" t="n">
-        <v>3.276439</v>
+        <v>3.309593</v>
       </c>
       <c r="D83" t="n">
-        <v>3.246719</v>
+        <v>3.2487</v>
       </c>
       <c r="E83" t="n">
-        <v>3.3</v>
+        <v>3.302047</v>
       </c>
     </row>
     <row r="84">
@@ -1772,16 +1772,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>3.224183</v>
+        <v>3.255916</v>
       </c>
       <c r="C84" t="n">
-        <v>3.276723</v>
+        <v>3.309501</v>
       </c>
       <c r="D84" t="n">
-        <v>3.246719</v>
+        <v>3.24856</v>
       </c>
       <c r="E84" t="n">
-        <v>3.3</v>
+        <v>3.301901</v>
       </c>
     </row>
     <row r="85">
@@ -1789,16 +1789,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>3.224451</v>
+        <v>3.255828</v>
       </c>
       <c r="C85" t="n">
-        <v>3.277</v>
+        <v>3.30941</v>
       </c>
       <c r="D85" t="n">
-        <v>3.246719</v>
+        <v>3.248429</v>
       </c>
       <c r="E85" t="n">
-        <v>3.3</v>
+        <v>3.301766</v>
       </c>
     </row>
     <row r="86">
@@ -1806,16 +1806,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>3.224713</v>
+        <v>3.25574</v>
       </c>
       <c r="C86" t="n">
-        <v>3.277271</v>
+        <v>3.309319</v>
       </c>
       <c r="D86" t="n">
-        <v>3.246719</v>
+        <v>3.248308</v>
       </c>
       <c r="E86" t="n">
-        <v>3.3</v>
+        <v>3.301641</v>
       </c>
     </row>
     <row r="87">
@@ -1823,16 +1823,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>3.224969</v>
+        <v>3.255653</v>
       </c>
       <c r="C87" t="n">
-        <v>3.277535</v>
+        <v>3.309229</v>
       </c>
       <c r="D87" t="n">
-        <v>3.246719</v>
+        <v>3.248195</v>
       </c>
       <c r="E87" t="n">
-        <v>3.3</v>
+        <v>3.301525</v>
       </c>
     </row>
     <row r="88">
@@ -1840,16 +1840,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>3.225219</v>
+        <v>3.255567</v>
       </c>
       <c r="C88" t="n">
-        <v>3.277793</v>
+        <v>3.30914</v>
       </c>
       <c r="D88" t="n">
-        <v>3.246719</v>
+        <v>3.24809</v>
       </c>
       <c r="E88" t="n">
-        <v>3.3</v>
+        <v>3.301416</v>
       </c>
     </row>
     <row r="89">
@@ -1857,16 +1857,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>3.225464</v>
+        <v>3.255481</v>
       </c>
       <c r="C89" t="n">
-        <v>3.278045</v>
+        <v>3.309052</v>
       </c>
       <c r="D89" t="n">
-        <v>3.246719</v>
+        <v>3.247993</v>
       </c>
       <c r="E89" t="n">
-        <v>3.3</v>
+        <v>3.301316</v>
       </c>
     </row>
     <row r="90">
@@ -1874,16 +1874,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>3.225702</v>
+        <v>3.255397</v>
       </c>
       <c r="C90" t="n">
-        <v>3.278292</v>
+        <v>3.308964</v>
       </c>
       <c r="D90" t="n">
-        <v>3.246719</v>
+        <v>3.247902</v>
       </c>
       <c r="E90" t="n">
-        <v>3.3</v>
+        <v>3.301223</v>
       </c>
     </row>
     <row r="91">
@@ -1891,16 +1891,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>3.225936</v>
+        <v>3.255313</v>
       </c>
       <c r="C91" t="n">
-        <v>3.278533</v>
+        <v>3.308878</v>
       </c>
       <c r="D91" t="n">
-        <v>3.246719</v>
+        <v>3.247818</v>
       </c>
       <c r="E91" t="n">
-        <v>3.3</v>
+        <v>3.301136</v>
       </c>
     </row>
     <row r="92">
@@ -1908,16 +1908,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>3.226164</v>
+        <v>3.25523</v>
       </c>
       <c r="C92" t="n">
-        <v>3.278769</v>
+        <v>3.308792</v>
       </c>
       <c r="D92" t="n">
-        <v>3.246719</v>
+        <v>3.24774</v>
       </c>
       <c r="E92" t="n">
-        <v>3.3</v>
+        <v>3.301055</v>
       </c>
     </row>
     <row r="93">
@@ -1925,16 +1925,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>3.226388</v>
+        <v>3.255148</v>
       </c>
       <c r="C93" t="n">
-        <v>3.279</v>
+        <v>3.308708</v>
       </c>
       <c r="D93" t="n">
-        <v>3.246719</v>
+        <v>3.247668</v>
       </c>
       <c r="E93" t="n">
-        <v>3.3</v>
+        <v>3.30098</v>
       </c>
     </row>
     <row r="94">
@@ -1942,16 +1942,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>3.226606</v>
+        <v>3.255067</v>
       </c>
       <c r="C94" t="n">
-        <v>3.279226</v>
+        <v>3.308624</v>
       </c>
       <c r="D94" t="n">
-        <v>3.246719</v>
+        <v>3.247601</v>
       </c>
       <c r="E94" t="n">
-        <v>3.3</v>
+        <v>3.300911</v>
       </c>
     </row>
     <row r="95">
@@ -1959,16 +1959,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>3.22682</v>
+        <v>3.254988</v>
       </c>
       <c r="C95" t="n">
-        <v>3.279447</v>
+        <v>3.308542</v>
       </c>
       <c r="D95" t="n">
-        <v>3.246719</v>
+        <v>3.247538</v>
       </c>
       <c r="E95" t="n">
-        <v>3.3</v>
+        <v>3.300846</v>
       </c>
     </row>
     <row r="96">
@@ -1976,16 +1976,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>3.22703</v>
+        <v>3.254909</v>
       </c>
       <c r="C96" t="n">
-        <v>3.279663</v>
+        <v>3.308461</v>
       </c>
       <c r="D96" t="n">
-        <v>3.246719</v>
+        <v>3.24748</v>
       </c>
       <c r="E96" t="n">
-        <v>3.3</v>
+        <v>3.300786</v>
       </c>
     </row>
     <row r="97">
@@ -1993,16 +1993,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>3.227235</v>
+        <v>3.254831</v>
       </c>
       <c r="C97" t="n">
-        <v>3.279875</v>
+        <v>3.30838</v>
       </c>
       <c r="D97" t="n">
-        <v>3.246719</v>
+        <v>3.247426</v>
       </c>
       <c r="E97" t="n">
-        <v>3.3</v>
+        <v>3.30073</v>
       </c>
     </row>
     <row r="98">
@@ -2010,16 +2010,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>3.227436</v>
+        <v>3.254755</v>
       </c>
       <c r="C98" t="n">
-        <v>3.280082</v>
+        <v>3.308301</v>
       </c>
       <c r="D98" t="n">
-        <v>3.246719</v>
+        <v>3.247376</v>
       </c>
       <c r="E98" t="n">
-        <v>3.3</v>
+        <v>3.300678</v>
       </c>
     </row>
     <row r="99">
@@ -2027,16 +2027,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>3.227633</v>
+        <v>3.254679</v>
       </c>
       <c r="C99" t="n">
-        <v>3.280286</v>
+        <v>3.308223</v>
       </c>
       <c r="D99" t="n">
-        <v>3.246719</v>
+        <v>3.247329</v>
       </c>
       <c r="E99" t="n">
-        <v>3.3</v>
+        <v>3.30063</v>
       </c>
     </row>
     <row r="100">
@@ -2044,16 +2044,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>3.227825</v>
+        <v>3.254605</v>
       </c>
       <c r="C100" t="n">
-        <v>3.280485</v>
+        <v>3.308146</v>
       </c>
       <c r="D100" t="n">
-        <v>3.246719</v>
+        <v>3.247286</v>
       </c>
       <c r="E100" t="n">
-        <v>3.3</v>
+        <v>3.300585</v>
       </c>
     </row>
     <row r="101">
@@ -2061,16 +2061,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>3.228014</v>
+        <v>3.254531</v>
       </c>
       <c r="C101" t="n">
-        <v>3.28068</v>
+        <v>3.30807</v>
       </c>
       <c r="D101" t="n">
-        <v>3.246719</v>
+        <v>3.247246</v>
       </c>
       <c r="E101" t="n">
-        <v>3.3</v>
+        <v>3.300544</v>
       </c>
     </row>
   </sheetData>
@@ -2112,10 +2112,10 @@
         <v>2.076</v>
       </c>
       <c r="D2" t="n">
-        <v>2.114314</v>
+        <v>2.054745</v>
       </c>
       <c r="E2" t="n">
-        <v>2.136824</v>
+        <v>2.076</v>
       </c>
     </row>
     <row r="3">
@@ -2129,10 +2129,10 @@
         <v>2.163032</v>
       </c>
       <c r="D3" t="n">
-        <v>2.361622</v>
+        <v>2.225195</v>
       </c>
       <c r="E3" t="n">
-        <v>2.38973</v>
+        <v>2.250137</v>
       </c>
     </row>
     <row r="4">
@@ -2146,10 +2146,10 @@
         <v>2.282858</v>
       </c>
       <c r="D4" t="n">
-        <v>2.590168</v>
+        <v>2.491632</v>
       </c>
       <c r="E4" t="n">
-        <v>2.624004</v>
+        <v>2.522932</v>
       </c>
     </row>
     <row r="5">
@@ -2163,10 +2163,10 @@
         <v>2.386292</v>
       </c>
       <c r="D5" t="n">
-        <v>2.736766</v>
+        <v>2.661487</v>
       </c>
       <c r="E5" t="n">
-        <v>2.77456</v>
+        <v>2.697221</v>
       </c>
     </row>
     <row r="6">
@@ -2180,10 +2180,10 @@
         <v>2.478759</v>
       </c>
       <c r="D6" t="n">
-        <v>2.876139</v>
+        <v>2.809621</v>
       </c>
       <c r="E6" t="n">
-        <v>2.917899</v>
+        <v>2.849463</v>
       </c>
     </row>
     <row r="7">
@@ -2197,10 +2197,10 @@
         <v>2.564868</v>
       </c>
       <c r="D7" t="n">
-        <v>3.044924</v>
+        <v>2.952482</v>
       </c>
       <c r="E7" t="n">
-        <v>3.091756</v>
+        <v>2.9965</v>
       </c>
     </row>
     <row r="8">
@@ -2214,10 +2214,10 @@
         <v>2.651038</v>
       </c>
       <c r="D8" t="n">
-        <v>3.16284</v>
+        <v>3.120388</v>
       </c>
       <c r="E8" t="n">
-        <v>3.213389</v>
+        <v>3.169583</v>
       </c>
     </row>
     <row r="9">
@@ -2231,10 +2231,10 @@
         <v>2.72399</v>
       </c>
       <c r="D9" t="n">
-        <v>3.219364</v>
+        <v>3.18485</v>
       </c>
       <c r="E9" t="n">
-        <v>3.271746</v>
+        <v>3.236109</v>
       </c>
     </row>
     <row r="10">
@@ -2248,10 +2248,10 @@
         <v>2.792521</v>
       </c>
       <c r="D10" t="n">
-        <v>3.377617</v>
+        <v>3.28777</v>
       </c>
       <c r="E10" t="n">
-        <v>3.435306</v>
+        <v>3.342415</v>
       </c>
     </row>
     <row r="11">
@@ -2265,10 +2265,10 @@
         <v>2.863084</v>
       </c>
       <c r="D11" t="n">
-        <v>3.454728</v>
+        <v>3.440462</v>
       </c>
       <c r="E11" t="n">
-        <v>3.515097</v>
+        <v>3.500331</v>
       </c>
     </row>
     <row r="12">
@@ -2282,10 +2282,10 @@
         <v>2.920817</v>
       </c>
       <c r="D12" t="n">
-        <v>3.445216</v>
+        <v>3.44008</v>
       </c>
       <c r="E12" t="n">
-        <v>3.505251</v>
+        <v>3.499935</v>
       </c>
     </row>
     <row r="13">
@@ -2299,10 +2299,10 @@
         <v>2.974789</v>
       </c>
       <c r="D13" t="n">
-        <v>3.60903</v>
+        <v>3.508089</v>
       </c>
       <c r="E13" t="n">
-        <v>3.674946</v>
+        <v>3.570349</v>
       </c>
     </row>
     <row r="14">
@@ -2316,10 +2316,10 @@
         <v>3.03333</v>
       </c>
       <c r="D14" t="n">
-        <v>3.653169</v>
+        <v>3.67024</v>
       </c>
       <c r="E14" t="n">
-        <v>3.720718</v>
+        <v>3.738425</v>
       </c>
     </row>
     <row r="15">
@@ -2327,16 +2327,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3.030049</v>
+        <v>3.026722</v>
       </c>
       <c r="C15" t="n">
-        <v>3.076422</v>
+        <v>3.072993</v>
       </c>
       <c r="D15" t="n">
-        <v>3.510313</v>
+        <v>3.527066</v>
       </c>
       <c r="E15" t="n">
-        <v>3.572651</v>
+        <v>3.590004</v>
       </c>
     </row>
     <row r="16">
@@ -2344,16 +2344,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3.059983</v>
+        <v>3.060078</v>
       </c>
       <c r="C16" t="n">
-        <v>3.107282</v>
+        <v>3.10738</v>
       </c>
       <c r="D16" t="n">
-        <v>3.463686</v>
+        <v>3.527066</v>
       </c>
       <c r="E16" t="n">
-        <v>3.524371</v>
+        <v>3.590004</v>
       </c>
     </row>
     <row r="17">
@@ -2361,16 +2361,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3.085215</v>
+        <v>3.084722</v>
       </c>
       <c r="C17" t="n">
-        <v>3.133301</v>
+        <v>3.132792</v>
       </c>
       <c r="D17" t="n">
-        <v>3.463208</v>
+        <v>3.454378</v>
       </c>
       <c r="E17" t="n">
-        <v>3.523875</v>
+        <v>3.514735</v>
       </c>
     </row>
     <row r="18">
@@ -2378,16 +2378,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3.107363</v>
+        <v>3.106466</v>
       </c>
       <c r="C18" t="n">
-        <v>3.156146</v>
+        <v>3.155221</v>
       </c>
       <c r="D18" t="n">
-        <v>3.459761</v>
+        <v>3.454378</v>
       </c>
       <c r="E18" t="n">
-        <v>3.520307</v>
+        <v>3.514735</v>
       </c>
     </row>
     <row r="19">
@@ -2395,16 +2395,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3.126778</v>
+        <v>3.125795</v>
       </c>
       <c r="C19" t="n">
-        <v>3.176175</v>
+        <v>3.175161</v>
       </c>
       <c r="D19" t="n">
-        <v>3.453427</v>
+        <v>3.454378</v>
       </c>
       <c r="E19" t="n">
-        <v>3.513751</v>
+        <v>3.514735</v>
       </c>
     </row>
     <row r="20">
@@ -2412,16 +2412,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.143741</v>
+        <v>3.143089</v>
       </c>
       <c r="C20" t="n">
-        <v>3.193679</v>
+        <v>3.193005</v>
       </c>
       <c r="D20" t="n">
-        <v>3.444269</v>
+        <v>3.454378</v>
       </c>
       <c r="E20" t="n">
-        <v>3.50427</v>
+        <v>3.514735</v>
       </c>
     </row>
     <row r="21">
@@ -2429,16 +2429,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3.158481</v>
+        <v>3.158653</v>
       </c>
       <c r="C21" t="n">
-        <v>3.20889</v>
+        <v>3.209068</v>
       </c>
       <c r="D21" t="n">
-        <v>3.432332</v>
+        <v>3.454378</v>
       </c>
       <c r="E21" t="n">
-        <v>3.491917</v>
+        <v>3.514735</v>
       </c>
     </row>
     <row r="22">
@@ -2446,16 +2446,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3.171212</v>
+        <v>3.161905</v>
       </c>
       <c r="C22" t="n">
-        <v>3.22203</v>
+        <v>3.212424</v>
       </c>
       <c r="D22" t="n">
-        <v>3.419465</v>
+        <v>3.226932</v>
       </c>
       <c r="E22" t="n">
-        <v>3.478601</v>
+        <v>3.279562</v>
       </c>
     </row>
     <row r="23">
@@ -2463,16 +2463,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3.18222</v>
+        <v>3.165023</v>
       </c>
       <c r="C23" t="n">
-        <v>3.233394</v>
+        <v>3.215643</v>
       </c>
       <c r="D23" t="n">
-        <v>3.407471</v>
+        <v>3.230518</v>
       </c>
       <c r="E23" t="n">
-        <v>3.46619</v>
+        <v>3.283266</v>
       </c>
     </row>
     <row r="24">
@@ -2480,16 +2480,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3.191768</v>
+        <v>3.167999</v>
       </c>
       <c r="C24" t="n">
-        <v>3.243251</v>
+        <v>3.218714</v>
       </c>
       <c r="D24" t="n">
-        <v>3.396291</v>
+        <v>3.233455</v>
       </c>
       <c r="E24" t="n">
-        <v>3.454624</v>
+        <v>3.286299</v>
       </c>
     </row>
     <row r="25">
@@ -2497,16 +2497,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3.20007</v>
+        <v>3.170826</v>
       </c>
       <c r="C25" t="n">
-        <v>3.251823</v>
+        <v>3.221632</v>
       </c>
       <c r="D25" t="n">
-        <v>3.385874</v>
+        <v>3.235859</v>
       </c>
       <c r="E25" t="n">
-        <v>3.443847</v>
+        <v>3.288783</v>
       </c>
     </row>
     <row r="26">
@@ -2514,16 +2514,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3.207306</v>
+        <v>3.173506</v>
       </c>
       <c r="C26" t="n">
-        <v>3.259294</v>
+        <v>3.224399</v>
       </c>
       <c r="D26" t="n">
-        <v>3.37617</v>
+        <v>3.237828</v>
       </c>
       <c r="E26" t="n">
-        <v>3.433809</v>
+        <v>3.290816</v>
       </c>
     </row>
     <row r="27">
@@ -2531,16 +2531,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3.213625</v>
+        <v>3.176042</v>
       </c>
       <c r="C27" t="n">
-        <v>3.265819</v>
+        <v>3.227017</v>
       </c>
       <c r="D27" t="n">
-        <v>3.367131</v>
+        <v>3.23944</v>
       </c>
       <c r="E27" t="n">
-        <v>3.42446</v>
+        <v>3.292481</v>
       </c>
     </row>
     <row r="28">
@@ -2548,16 +2548,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3.219152</v>
+        <v>3.178439</v>
       </c>
       <c r="C28" t="n">
-        <v>3.271527</v>
+        <v>3.229491</v>
       </c>
       <c r="D28" t="n">
-        <v>3.358713</v>
+        <v>3.240759</v>
       </c>
       <c r="E28" t="n">
-        <v>3.415755</v>
+        <v>3.293844</v>
       </c>
     </row>
     <row r="29">
@@ -2565,16 +2565,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3.223995</v>
+        <v>3.180703</v>
       </c>
       <c r="C29" t="n">
-        <v>3.276529</v>
+        <v>3.231828</v>
       </c>
       <c r="D29" t="n">
-        <v>3.350876</v>
+        <v>3.24184</v>
       </c>
       <c r="E29" t="n">
-        <v>3.40765</v>
+        <v>3.29496</v>
       </c>
     </row>
     <row r="30">
@@ -2582,16 +2582,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3.228243</v>
+        <v>3.182842</v>
       </c>
       <c r="C30" t="n">
-        <v>3.280916</v>
+        <v>3.234036</v>
       </c>
       <c r="D30" t="n">
-        <v>3.343579</v>
+        <v>3.242724</v>
       </c>
       <c r="E30" t="n">
-        <v>3.400105</v>
+        <v>3.295873</v>
       </c>
     </row>
     <row r="31">
@@ -2599,16 +2599,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3.231973</v>
+        <v>3.184862</v>
       </c>
       <c r="C31" t="n">
-        <v>3.284768</v>
+        <v>3.236122</v>
       </c>
       <c r="D31" t="n">
-        <v>3.336787</v>
+        <v>3.243448</v>
       </c>
       <c r="E31" t="n">
-        <v>3.393083</v>
+        <v>3.296621</v>
       </c>
     </row>
     <row r="32">
@@ -2616,16 +2616,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3.235251</v>
+        <v>3.186771</v>
       </c>
       <c r="C32" t="n">
-        <v>3.288154</v>
+        <v>3.238092</v>
       </c>
       <c r="D32" t="n">
-        <v>3.330467</v>
+        <v>3.244041</v>
       </c>
       <c r="E32" t="n">
-        <v>3.386547</v>
+        <v>3.297234</v>
       </c>
     </row>
     <row r="33">
@@ -2633,16 +2633,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3.238133</v>
+        <v>3.188576</v>
       </c>
       <c r="C33" t="n">
-        <v>3.291131</v>
+        <v>3.239956</v>
       </c>
       <c r="D33" t="n">
-        <v>3.324584</v>
+        <v>3.244527</v>
       </c>
       <c r="E33" t="n">
-        <v>3.380466</v>
+        <v>3.297735</v>
       </c>
     </row>
     <row r="34">
@@ -2650,16 +2650,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3.240669</v>
+        <v>3.190284</v>
       </c>
       <c r="C34" t="n">
-        <v>3.293751</v>
+        <v>3.241719</v>
       </c>
       <c r="D34" t="n">
-        <v>3.319111</v>
+        <v>3.244924</v>
       </c>
       <c r="E34" t="n">
-        <v>3.374808</v>
+        <v>3.298146</v>
       </c>
     </row>
     <row r="35">
@@ -2667,16 +2667,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3.2429</v>
+        <v>3.1919</v>
       </c>
       <c r="C35" t="n">
-        <v>3.296055</v>
+        <v>3.243388</v>
       </c>
       <c r="D35" t="n">
-        <v>3.314019</v>
+        <v>3.245249</v>
       </c>
       <c r="E35" t="n">
-        <v>3.369545</v>
+        <v>3.298482</v>
       </c>
     </row>
     <row r="36">
@@ -2684,16 +2684,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3.244864</v>
+        <v>3.193432</v>
       </c>
       <c r="C36" t="n">
-        <v>3.298084</v>
+        <v>3.244969</v>
       </c>
       <c r="D36" t="n">
-        <v>3.309283</v>
+        <v>3.245516</v>
       </c>
       <c r="E36" t="n">
-        <v>3.364648</v>
+        <v>3.298757</v>
       </c>
     </row>
     <row r="37">
@@ -2701,16 +2701,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3.246591</v>
+        <v>3.194885</v>
       </c>
       <c r="C37" t="n">
-        <v>3.299868</v>
+        <v>3.246469</v>
       </c>
       <c r="D37" t="n">
-        <v>3.304877</v>
+        <v>3.245734</v>
       </c>
       <c r="E37" t="n">
-        <v>3.360094</v>
+        <v>3.298982</v>
       </c>
     </row>
     <row r="38">
@@ -2718,16 +2718,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3.248111</v>
+        <v>3.196264</v>
       </c>
       <c r="C38" t="n">
-        <v>3.301437</v>
+        <v>3.247893</v>
       </c>
       <c r="D38" t="n">
-        <v>3.300778</v>
+        <v>3.245912</v>
       </c>
       <c r="E38" t="n">
-        <v>3.355859</v>
+        <v>3.299167</v>
       </c>
     </row>
     <row r="39">
@@ -2735,16 +2735,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3.249446</v>
+        <v>3.197574</v>
       </c>
       <c r="C39" t="n">
-        <v>3.302817</v>
+        <v>3.249246</v>
       </c>
       <c r="D39" t="n">
-        <v>3.296967</v>
+        <v>3.246059</v>
       </c>
       <c r="E39" t="n">
-        <v>3.351919</v>
+        <v>3.299318</v>
       </c>
     </row>
     <row r="40">
@@ -2752,16 +2752,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3.250618</v>
+        <v>3.198821</v>
       </c>
       <c r="C40" t="n">
-        <v>3.304028</v>
+        <v>3.250533</v>
       </c>
       <c r="D40" t="n">
-        <v>3.293423</v>
+        <v>3.246178</v>
       </c>
       <c r="E40" t="n">
-        <v>3.348256</v>
+        <v>3.299441</v>
       </c>
     </row>
     <row r="41">
@@ -2769,16 +2769,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3.251647</v>
+        <v>3.200007</v>
       </c>
       <c r="C41" t="n">
-        <v>3.30509</v>
+        <v>3.251758</v>
       </c>
       <c r="D41" t="n">
-        <v>3.290127</v>
+        <v>3.246276</v>
       </c>
       <c r="E41" t="n">
-        <v>3.34485</v>
+        <v>3.299543</v>
       </c>
     </row>
     <row r="42">
@@ -2786,16 +2786,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3.252547</v>
+        <v>3.201138</v>
       </c>
       <c r="C42" t="n">
-        <v>3.306021</v>
+        <v>3.252925</v>
       </c>
       <c r="D42" t="n">
-        <v>3.287063</v>
+        <v>3.246357</v>
       </c>
       <c r="E42" t="n">
-        <v>3.341683</v>
+        <v>3.299626</v>
       </c>
     </row>
     <row r="43">
@@ -2803,16 +2803,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3.253335</v>
+        <v>3.202216</v>
       </c>
       <c r="C43" t="n">
-        <v>3.306834</v>
+        <v>3.254038</v>
       </c>
       <c r="D43" t="n">
-        <v>3.284213</v>
+        <v>3.246422</v>
       </c>
       <c r="E43" t="n">
-        <v>3.338739</v>
+        <v>3.299693</v>
       </c>
     </row>
     <row r="44">
@@ -2820,16 +2820,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3.254022</v>
+        <v>3.203245</v>
       </c>
       <c r="C44" t="n">
-        <v>3.307544</v>
+        <v>3.255101</v>
       </c>
       <c r="D44" t="n">
-        <v>3.281564</v>
+        <v>3.246476</v>
       </c>
       <c r="E44" t="n">
-        <v>3.336001</v>
+        <v>3.299749</v>
       </c>
     </row>
     <row r="45">
@@ -2837,16 +2837,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3.254619</v>
+        <v>3.204229</v>
       </c>
       <c r="C45" t="n">
-        <v>3.308161</v>
+        <v>3.256117</v>
       </c>
       <c r="D45" t="n">
-        <v>3.279102</v>
+        <v>3.24652</v>
       </c>
       <c r="E45" t="n">
-        <v>3.333457</v>
+        <v>3.299795</v>
       </c>
     </row>
     <row r="46">
@@ -2854,16 +2854,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3.255138</v>
+        <v>3.205169</v>
       </c>
       <c r="C46" t="n">
-        <v>3.308697</v>
+        <v>3.257088</v>
       </c>
       <c r="D46" t="n">
-        <v>3.276812</v>
+        <v>3.246556</v>
       </c>
       <c r="E46" t="n">
-        <v>3.331091</v>
+        <v>3.299832</v>
       </c>
     </row>
     <row r="47">
@@ -2871,16 +2871,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3.255586</v>
+        <v>3.20607</v>
       </c>
       <c r="C47" t="n">
-        <v>3.30916</v>
+        <v>3.258018</v>
       </c>
       <c r="D47" t="n">
-        <v>3.274684</v>
+        <v>3.246586</v>
       </c>
       <c r="E47" t="n">
-        <v>3.328892</v>
+        <v>3.299862</v>
       </c>
     </row>
     <row r="48">
@@ -2888,16 +2888,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3.255971</v>
+        <v>3.206932</v>
       </c>
       <c r="C48" t="n">
-        <v>3.309557</v>
+        <v>3.258908</v>
       </c>
       <c r="D48" t="n">
-        <v>3.272706</v>
+        <v>3.24661</v>
       </c>
       <c r="E48" t="n">
-        <v>3.326848</v>
+        <v>3.299887</v>
       </c>
     </row>
     <row r="49">
@@ -2905,16 +2905,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3.2563</v>
+        <v>3.207759</v>
       </c>
       <c r="C49" t="n">
-        <v>3.309897</v>
+        <v>3.259762</v>
       </c>
       <c r="D49" t="n">
-        <v>3.270867</v>
+        <v>3.24663</v>
       </c>
       <c r="E49" t="n">
-        <v>3.324948</v>
+        <v>3.299908</v>
       </c>
     </row>
     <row r="50">
@@ -2922,16 +2922,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3.25658</v>
+        <v>3.208553</v>
       </c>
       <c r="C50" t="n">
-        <v>3.310186</v>
+        <v>3.260582</v>
       </c>
       <c r="D50" t="n">
-        <v>3.269158</v>
+        <v>3.246646</v>
       </c>
       <c r="E50" t="n">
-        <v>3.323182</v>
+        <v>3.299924</v>
       </c>
     </row>
     <row r="51">
@@ -2939,16 +2939,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3.256815</v>
+        <v>3.209315</v>
       </c>
       <c r="C51" t="n">
-        <v>3.31043</v>
+        <v>3.261369</v>
       </c>
       <c r="D51" t="n">
-        <v>3.26757</v>
+        <v>3.246659</v>
       </c>
       <c r="E51" t="n">
-        <v>3.321541</v>
+        <v>3.299938</v>
       </c>
     </row>
     <row r="52">
@@ -2956,16 +2956,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3.257011</v>
+        <v>3.210047</v>
       </c>
       <c r="C52" t="n">
-        <v>3.310632</v>
+        <v>3.262125</v>
       </c>
       <c r="D52" t="n">
-        <v>3.266094</v>
+        <v>3.24667</v>
       </c>
       <c r="E52" t="n">
-        <v>3.320016</v>
+        <v>3.299949</v>
       </c>
     </row>
     <row r="53">
@@ -2973,16 +2973,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3.257173</v>
+        <v>3.210752</v>
       </c>
       <c r="C53" t="n">
-        <v>3.310799</v>
+        <v>3.262853</v>
       </c>
       <c r="D53" t="n">
-        <v>3.264722</v>
+        <v>3.246679</v>
       </c>
       <c r="E53" t="n">
-        <v>3.318599</v>
+        <v>3.299959</v>
       </c>
     </row>
     <row r="54">
@@ -2990,16 +2990,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>3.257303</v>
+        <v>3.21143</v>
       </c>
       <c r="C54" t="n">
-        <v>3.310934</v>
+        <v>3.263553</v>
       </c>
       <c r="D54" t="n">
-        <v>3.263447</v>
+        <v>3.246686</v>
       </c>
       <c r="E54" t="n">
-        <v>3.317281</v>
+        <v>3.299966</v>
       </c>
     </row>
     <row r="55">
@@ -3007,16 +3007,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3.257405</v>
+        <v>3.212083</v>
       </c>
       <c r="C55" t="n">
-        <v>3.31104</v>
+        <v>3.264227</v>
       </c>
       <c r="D55" t="n">
-        <v>3.262262</v>
+        <v>3.246692</v>
       </c>
       <c r="E55" t="n">
-        <v>3.316057</v>
+        <v>3.299972</v>
       </c>
     </row>
     <row r="56">
@@ -3024,16 +3024,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>3.257484</v>
+        <v>3.212712</v>
       </c>
       <c r="C56" t="n">
-        <v>3.31112</v>
+        <v>3.264877</v>
       </c>
       <c r="D56" t="n">
-        <v>3.261161</v>
+        <v>3.246697</v>
       </c>
       <c r="E56" t="n">
-        <v>3.314919</v>
+        <v>3.299977</v>
       </c>
     </row>
     <row r="57">
@@ -3041,16 +3041,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>3.25754</v>
+        <v>3.213319</v>
       </c>
       <c r="C57" t="n">
-        <v>3.311179</v>
+        <v>3.265504</v>
       </c>
       <c r="D57" t="n">
-        <v>3.260137</v>
+        <v>3.246701</v>
       </c>
       <c r="E57" t="n">
-        <v>3.313862</v>
+        <v>3.299981</v>
       </c>
     </row>
     <row r="58">
@@ -3058,16 +3058,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>3.257577</v>
+        <v>3.213905</v>
       </c>
       <c r="C58" t="n">
-        <v>3.311217</v>
+        <v>3.266108</v>
       </c>
       <c r="D58" t="n">
-        <v>3.259186</v>
+        <v>3.246704</v>
       </c>
       <c r="E58" t="n">
-        <v>3.31288</v>
+        <v>3.299985</v>
       </c>
     </row>
     <row r="59">
@@ -3075,16 +3075,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>3.257597</v>
+        <v>3.21447</v>
       </c>
       <c r="C59" t="n">
-        <v>3.311238</v>
+        <v>3.266693</v>
       </c>
       <c r="D59" t="n">
-        <v>3.258303</v>
+        <v>3.246707</v>
       </c>
       <c r="E59" t="n">
-        <v>3.311967</v>
+        <v>3.299988</v>
       </c>
     </row>
     <row r="60">
@@ -3092,16 +3092,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>3.257602</v>
+        <v>3.215017</v>
       </c>
       <c r="C60" t="n">
-        <v>3.311243</v>
+        <v>3.267257</v>
       </c>
       <c r="D60" t="n">
-        <v>3.257482</v>
+        <v>3.246709</v>
       </c>
       <c r="E60" t="n">
-        <v>3.311118</v>
+        <v>3.29999</v>
       </c>
     </row>
     <row r="61">
@@ -3109,16 +3109,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>3.257594</v>
+        <v>3.215545</v>
       </c>
       <c r="C61" t="n">
-        <v>3.311234</v>
+        <v>3.267802</v>
       </c>
       <c r="D61" t="n">
-        <v>3.256719</v>
+        <v>3.246711</v>
       </c>
       <c r="E61" t="n">
-        <v>3.31033</v>
+        <v>3.299992</v>
       </c>
     </row>
     <row r="62">
@@ -3126,16 +3126,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>3.257573</v>
+        <v>3.216056</v>
       </c>
       <c r="C62" t="n">
-        <v>3.311213</v>
+        <v>3.26833</v>
       </c>
       <c r="D62" t="n">
-        <v>3.25601</v>
+        <v>3.246712</v>
       </c>
       <c r="E62" t="n">
-        <v>3.309598</v>
+        <v>3.299993</v>
       </c>
     </row>
     <row r="63">
@@ -3143,16 +3143,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>3.257543</v>
+        <v>3.21655</v>
       </c>
       <c r="C63" t="n">
-        <v>3.311182</v>
+        <v>3.268841</v>
       </c>
       <c r="D63" t="n">
-        <v>3.255351</v>
+        <v>3.246714</v>
       </c>
       <c r="E63" t="n">
-        <v>3.308917</v>
+        <v>3.299994</v>
       </c>
     </row>
     <row r="64">
@@ -3160,16 +3160,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>3.257503</v>
+        <v>3.217029</v>
       </c>
       <c r="C64" t="n">
-        <v>3.311141</v>
+        <v>3.269335</v>
       </c>
       <c r="D64" t="n">
-        <v>3.254739</v>
+        <v>3.246715</v>
       </c>
       <c r="E64" t="n">
-        <v>3.308285</v>
+        <v>3.299995</v>
       </c>
     </row>
     <row r="65">
@@ -3177,16 +3177,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>3.257455</v>
+        <v>3.217493</v>
       </c>
       <c r="C65" t="n">
-        <v>3.311091</v>
+        <v>3.269814</v>
       </c>
       <c r="D65" t="n">
-        <v>3.25417</v>
+        <v>3.246715</v>
       </c>
       <c r="E65" t="n">
-        <v>3.307697</v>
+        <v>3.299996</v>
       </c>
     </row>
     <row r="66">
@@ -3194,16 +3194,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>3.257401</v>
+        <v>3.217943</v>
       </c>
       <c r="C66" t="n">
-        <v>3.311035</v>
+        <v>3.270278</v>
       </c>
       <c r="D66" t="n">
-        <v>3.253642</v>
+        <v>3.246716</v>
       </c>
       <c r="E66" t="n">
-        <v>3.307151</v>
+        <v>3.299997</v>
       </c>
     </row>
     <row r="67">
@@ -3211,16 +3211,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>3.25734</v>
+        <v>3.218379</v>
       </c>
       <c r="C67" t="n">
-        <v>3.310972</v>
+        <v>3.270729</v>
       </c>
       <c r="D67" t="n">
-        <v>3.253151</v>
+        <v>3.246717</v>
       </c>
       <c r="E67" t="n">
-        <v>3.306644</v>
+        <v>3.299997</v>
       </c>
     </row>
     <row r="68">
@@ -3228,16 +3228,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>3.257274</v>
+        <v>3.218802</v>
       </c>
       <c r="C68" t="n">
-        <v>3.310904</v>
+        <v>3.271165</v>
       </c>
       <c r="D68" t="n">
-        <v>3.252695</v>
+        <v>3.246717</v>
       </c>
       <c r="E68" t="n">
-        <v>3.306173</v>
+        <v>3.299998</v>
       </c>
     </row>
     <row r="69">
@@ -3245,16 +3245,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>3.257204</v>
+        <v>3.219212</v>
       </c>
       <c r="C69" t="n">
-        <v>3.310831</v>
+        <v>3.271589</v>
       </c>
       <c r="D69" t="n">
-        <v>3.252271</v>
+        <v>3.246717</v>
       </c>
       <c r="E69" t="n">
-        <v>3.305735</v>
+        <v>3.299998</v>
       </c>
     </row>
     <row r="70">
@@ -3262,16 +3262,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>3.257129</v>
+        <v>3.219611</v>
       </c>
       <c r="C70" t="n">
-        <v>3.310754</v>
+        <v>3.272001</v>
       </c>
       <c r="D70" t="n">
-        <v>3.251877</v>
+        <v>3.246718</v>
       </c>
       <c r="E70" t="n">
-        <v>3.305328</v>
+        <v>3.299999</v>
       </c>
     </row>
     <row r="71">
@@ -3279,16 +3279,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>3.257052</v>
+        <v>3.219998</v>
       </c>
       <c r="C71" t="n">
-        <v>3.310674</v>
+        <v>3.272401</v>
       </c>
       <c r="D71" t="n">
-        <v>3.251511</v>
+        <v>3.246718</v>
       </c>
       <c r="E71" t="n">
-        <v>3.30495</v>
+        <v>3.299999</v>
       </c>
     </row>
     <row r="72">
@@ -3296,16 +3296,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>3.256971</v>
+        <v>3.220374</v>
       </c>
       <c r="C72" t="n">
-        <v>3.310591</v>
+        <v>3.27279</v>
       </c>
       <c r="D72" t="n">
-        <v>3.251171</v>
+        <v>3.246718</v>
       </c>
       <c r="E72" t="n">
-        <v>3.304599</v>
+        <v>3.299999</v>
       </c>
     </row>
     <row r="73">
@@ -3313,16 +3313,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>3.256888</v>
+        <v>3.22074</v>
       </c>
       <c r="C73" t="n">
-        <v>3.310505</v>
+        <v>3.273167</v>
       </c>
       <c r="D73" t="n">
-        <v>3.250855</v>
+        <v>3.246718</v>
       </c>
       <c r="E73" t="n">
-        <v>3.304273</v>
+        <v>3.299999</v>
       </c>
     </row>
     <row r="74">
@@ -3330,16 +3330,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>3.256804</v>
+        <v>3.221096</v>
       </c>
       <c r="C74" t="n">
-        <v>3.310418</v>
+        <v>3.273535</v>
       </c>
       <c r="D74" t="n">
-        <v>3.250562</v>
+        <v>3.246718</v>
       </c>
       <c r="E74" t="n">
-        <v>3.30397</v>
+        <v>3.299999</v>
       </c>
     </row>
     <row r="75">
@@ -3347,16 +3347,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>3.256717</v>
+        <v>3.221442</v>
       </c>
       <c r="C75" t="n">
-        <v>3.310329</v>
+        <v>3.273892</v>
       </c>
       <c r="D75" t="n">
-        <v>3.250289</v>
+        <v>3.246719</v>
       </c>
       <c r="E75" t="n">
-        <v>3.303688</v>
+        <v>3.299999</v>
       </c>
     </row>
     <row r="76">
@@ -3364,16 +3364,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>3.25663</v>
+        <v>3.221779</v>
       </c>
       <c r="C76" t="n">
-        <v>3.310239</v>
+        <v>3.274241</v>
       </c>
       <c r="D76" t="n">
-        <v>3.250036</v>
+        <v>3.246719</v>
       </c>
       <c r="E76" t="n">
-        <v>3.303426</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="77">
@@ -3381,16 +3381,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>3.256542</v>
+        <v>3.222107</v>
       </c>
       <c r="C77" t="n">
-        <v>3.310147</v>
+        <v>3.274579</v>
       </c>
       <c r="D77" t="n">
-        <v>3.2498</v>
+        <v>3.246719</v>
       </c>
       <c r="E77" t="n">
-        <v>3.303183</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="78">
@@ -3398,16 +3398,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>3.256453</v>
+        <v>3.222427</v>
       </c>
       <c r="C78" t="n">
-        <v>3.310055</v>
+        <v>3.27491</v>
       </c>
       <c r="D78" t="n">
-        <v>3.249582</v>
+        <v>3.246719</v>
       </c>
       <c r="E78" t="n">
-        <v>3.302957</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="79">
@@ -3415,16 +3415,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>3.256363</v>
+        <v>3.222739</v>
       </c>
       <c r="C79" t="n">
-        <v>3.309963</v>
+        <v>3.275231</v>
       </c>
       <c r="D79" t="n">
-        <v>3.249379</v>
+        <v>3.246719</v>
       </c>
       <c r="E79" t="n">
-        <v>3.302747</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="80">
@@ -3432,16 +3432,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>3.256274</v>
+        <v>3.223042</v>
       </c>
       <c r="C80" t="n">
-        <v>3.30987</v>
+        <v>3.275545</v>
       </c>
       <c r="D80" t="n">
-        <v>3.24919</v>
+        <v>3.246719</v>
       </c>
       <c r="E80" t="n">
-        <v>3.302552</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="81">
@@ -3449,16 +3449,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>3.256184</v>
+        <v>3.223338</v>
       </c>
       <c r="C81" t="n">
-        <v>3.309778</v>
+        <v>3.27585</v>
       </c>
       <c r="D81" t="n">
-        <v>3.249015</v>
+        <v>3.246719</v>
       </c>
       <c r="E81" t="n">
-        <v>3.302371</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="82">
@@ -3466,16 +3466,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>3.256094</v>
+        <v>3.223627</v>
       </c>
       <c r="C82" t="n">
-        <v>3.309685</v>
+        <v>3.276148</v>
       </c>
       <c r="D82" t="n">
-        <v>3.248852</v>
+        <v>3.246719</v>
       </c>
       <c r="E82" t="n">
-        <v>3.302203</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="83">
@@ -3483,16 +3483,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>3.256005</v>
+        <v>3.223908</v>
       </c>
       <c r="C83" t="n">
-        <v>3.309593</v>
+        <v>3.276439</v>
       </c>
       <c r="D83" t="n">
-        <v>3.2487</v>
+        <v>3.246719</v>
       </c>
       <c r="E83" t="n">
-        <v>3.302047</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="84">
@@ -3500,16 +3500,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>3.255916</v>
+        <v>3.224183</v>
       </c>
       <c r="C84" t="n">
-        <v>3.309501</v>
+        <v>3.276723</v>
       </c>
       <c r="D84" t="n">
-        <v>3.24856</v>
+        <v>3.246719</v>
       </c>
       <c r="E84" t="n">
-        <v>3.301901</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="85">
@@ -3517,16 +3517,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>3.255828</v>
+        <v>3.224451</v>
       </c>
       <c r="C85" t="n">
-        <v>3.30941</v>
+        <v>3.277</v>
       </c>
       <c r="D85" t="n">
-        <v>3.248429</v>
+        <v>3.246719</v>
       </c>
       <c r="E85" t="n">
-        <v>3.301766</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="86">
@@ -3534,16 +3534,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>3.25574</v>
+        <v>3.224713</v>
       </c>
       <c r="C86" t="n">
-        <v>3.309319</v>
+        <v>3.277271</v>
       </c>
       <c r="D86" t="n">
-        <v>3.248308</v>
+        <v>3.246719</v>
       </c>
       <c r="E86" t="n">
-        <v>3.301641</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="87">
@@ -3551,16 +3551,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>3.255653</v>
+        <v>3.224969</v>
       </c>
       <c r="C87" t="n">
-        <v>3.309229</v>
+        <v>3.277535</v>
       </c>
       <c r="D87" t="n">
-        <v>3.248195</v>
+        <v>3.246719</v>
       </c>
       <c r="E87" t="n">
-        <v>3.301525</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="88">
@@ -3568,16 +3568,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>3.255567</v>
+        <v>3.225219</v>
       </c>
       <c r="C88" t="n">
-        <v>3.30914</v>
+        <v>3.277793</v>
       </c>
       <c r="D88" t="n">
-        <v>3.24809</v>
+        <v>3.246719</v>
       </c>
       <c r="E88" t="n">
-        <v>3.301416</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="89">
@@ -3585,16 +3585,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>3.255481</v>
+        <v>3.225464</v>
       </c>
       <c r="C89" t="n">
-        <v>3.309052</v>
+        <v>3.278045</v>
       </c>
       <c r="D89" t="n">
-        <v>3.247993</v>
+        <v>3.246719</v>
       </c>
       <c r="E89" t="n">
-        <v>3.301316</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="90">
@@ -3602,16 +3602,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>3.255397</v>
+        <v>3.225702</v>
       </c>
       <c r="C90" t="n">
-        <v>3.308964</v>
+        <v>3.278292</v>
       </c>
       <c r="D90" t="n">
-        <v>3.247902</v>
+        <v>3.246719</v>
       </c>
       <c r="E90" t="n">
-        <v>3.301223</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="91">
@@ -3619,16 +3619,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>3.255313</v>
+        <v>3.225936</v>
       </c>
       <c r="C91" t="n">
-        <v>3.308878</v>
+        <v>3.278533</v>
       </c>
       <c r="D91" t="n">
-        <v>3.247818</v>
+        <v>3.246719</v>
       </c>
       <c r="E91" t="n">
-        <v>3.301136</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="92">
@@ -3636,16 +3636,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>3.25523</v>
+        <v>3.226164</v>
       </c>
       <c r="C92" t="n">
-        <v>3.308792</v>
+        <v>3.278769</v>
       </c>
       <c r="D92" t="n">
-        <v>3.24774</v>
+        <v>3.246719</v>
       </c>
       <c r="E92" t="n">
-        <v>3.301055</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="93">
@@ -3653,16 +3653,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>3.255148</v>
+        <v>3.226388</v>
       </c>
       <c r="C93" t="n">
-        <v>3.308708</v>
+        <v>3.279</v>
       </c>
       <c r="D93" t="n">
-        <v>3.247668</v>
+        <v>3.246719</v>
       </c>
       <c r="E93" t="n">
-        <v>3.30098</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="94">
@@ -3670,16 +3670,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>3.255067</v>
+        <v>3.226606</v>
       </c>
       <c r="C94" t="n">
-        <v>3.308624</v>
+        <v>3.279226</v>
       </c>
       <c r="D94" t="n">
-        <v>3.247601</v>
+        <v>3.246719</v>
       </c>
       <c r="E94" t="n">
-        <v>3.300911</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="95">
@@ -3687,16 +3687,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>3.254988</v>
+        <v>3.22682</v>
       </c>
       <c r="C95" t="n">
-        <v>3.308542</v>
+        <v>3.279447</v>
       </c>
       <c r="D95" t="n">
-        <v>3.247538</v>
+        <v>3.246719</v>
       </c>
       <c r="E95" t="n">
-        <v>3.300846</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="96">
@@ -3704,16 +3704,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>3.254909</v>
+        <v>3.22703</v>
       </c>
       <c r="C96" t="n">
-        <v>3.308461</v>
+        <v>3.279663</v>
       </c>
       <c r="D96" t="n">
-        <v>3.24748</v>
+        <v>3.246719</v>
       </c>
       <c r="E96" t="n">
-        <v>3.300786</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="97">
@@ -3721,16 +3721,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>3.254831</v>
+        <v>3.227235</v>
       </c>
       <c r="C97" t="n">
-        <v>3.30838</v>
+        <v>3.279875</v>
       </c>
       <c r="D97" t="n">
-        <v>3.247426</v>
+        <v>3.246719</v>
       </c>
       <c r="E97" t="n">
-        <v>3.30073</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="98">
@@ -3738,16 +3738,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>3.254755</v>
+        <v>3.227436</v>
       </c>
       <c r="C98" t="n">
-        <v>3.308301</v>
+        <v>3.280082</v>
       </c>
       <c r="D98" t="n">
-        <v>3.247376</v>
+        <v>3.246719</v>
       </c>
       <c r="E98" t="n">
-        <v>3.300678</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="99">
@@ -3755,16 +3755,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>3.254679</v>
+        <v>3.227633</v>
       </c>
       <c r="C99" t="n">
-        <v>3.308223</v>
+        <v>3.280286</v>
       </c>
       <c r="D99" t="n">
-        <v>3.247329</v>
+        <v>3.246719</v>
       </c>
       <c r="E99" t="n">
-        <v>3.30063</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="100">
@@ -3772,16 +3772,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>3.254605</v>
+        <v>3.227825</v>
       </c>
       <c r="C100" t="n">
-        <v>3.308146</v>
+        <v>3.280485</v>
       </c>
       <c r="D100" t="n">
-        <v>3.247286</v>
+        <v>3.246719</v>
       </c>
       <c r="E100" t="n">
-        <v>3.300585</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="101">
@@ -3789,16 +3789,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>3.254531</v>
+        <v>3.228014</v>
       </c>
       <c r="C101" t="n">
-        <v>3.30807</v>
+        <v>3.28068</v>
       </c>
       <c r="D101" t="n">
-        <v>3.247246</v>
+        <v>3.246719</v>
       </c>
       <c r="E101" t="n">
-        <v>3.300544</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
